--- a/MCP_I2C/testy_I2C_AVR.xlsx
+++ b/MCP_I2C/testy_I2C_AVR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafal\Desktop\studia II st\praca magisterska\MCP_I2C\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F14EAB7-2126-4DAE-8724-651A857A0B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD4B256-27C6-404F-9974-6B491F55F432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5055" yWindow="2295" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="8">
   <si>
     <t>rezystor 1kOhm</t>
   </si>
@@ -383,15 +383,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C5:E45"/>
+  <dimension ref="C5:J45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="18.140625" customWidth="1"/>
     <col min="5" max="5" width="18.85546875" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
+    <col min="10" max="10" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
@@ -401,8 +404,17 @@
       <c r="E5" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
@@ -412,8 +424,17 @@
       <c r="E6" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C7" s="1">
         <v>5</v>
       </c>
@@ -423,8 +444,17 @@
       <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="8" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H7" s="1">
+        <v>7</v>
+      </c>
+      <c r="I7" s="2">
+        <v>100000</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C8" s="1">
         <v>5</v>
       </c>
@@ -434,8 +464,17 @@
       <c r="E8" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H8" s="1">
+        <v>7</v>
+      </c>
+      <c r="I8" s="2">
+        <v>200000</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C9" s="1">
         <v>5</v>
       </c>
@@ -445,8 +484,17 @@
       <c r="E9" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H9" s="1">
+        <v>7</v>
+      </c>
+      <c r="I9" s="2">
+        <v>300000</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -456,8 +504,17 @@
       <c r="E10" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H10" s="1">
+        <v>7</v>
+      </c>
+      <c r="I10" s="2">
+        <v>400000</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C11" s="1">
         <v>5</v>
       </c>
@@ -467,8 +524,17 @@
       <c r="E11" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H11" s="1">
+        <v>7</v>
+      </c>
+      <c r="I11" s="2">
+        <v>500000</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C12" s="1">
         <v>5</v>
       </c>
@@ -478,8 +544,17 @@
       <c r="E12" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H12" s="1">
+        <v>7</v>
+      </c>
+      <c r="I12" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C13" s="1">
         <v>5</v>
       </c>
@@ -489,8 +564,17 @@
       <c r="E13" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H13" s="1">
+        <v>7</v>
+      </c>
+      <c r="I13" s="2">
+        <v>700000</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C14" s="1">
         <v>5</v>
       </c>
@@ -500,8 +584,17 @@
       <c r="E14" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H14" s="1">
+        <v>7</v>
+      </c>
+      <c r="I14" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C15" s="1">
         <v>5</v>
       </c>
@@ -511,8 +604,17 @@
       <c r="E15" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H15" s="1">
+        <v>7</v>
+      </c>
+      <c r="I15" s="2">
+        <v>900000</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C16" s="1">
         <v>5</v>
       </c>
@@ -522,8 +624,17 @@
       <c r="E16" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H16" s="1">
+        <v>7</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C20" s="1" t="s">
         <v>5</v>
       </c>
@@ -533,8 +644,17 @@
       <c r="E20" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C21" s="1" t="s">
         <v>1</v>
       </c>
@@ -544,8 +664,17 @@
       <c r="E21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C22" s="1">
         <v>3</v>
       </c>
@@ -555,8 +684,17 @@
       <c r="E22" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H22" s="1">
+        <v>10</v>
+      </c>
+      <c r="I22" s="2">
+        <v>100000</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C23" s="1">
         <v>3</v>
       </c>
@@ -566,8 +704,17 @@
       <c r="E23" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H23" s="1">
+        <v>10</v>
+      </c>
+      <c r="I23" s="2">
+        <v>200000</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C24" s="1">
         <v>3</v>
       </c>
@@ -577,8 +724,17 @@
       <c r="E24" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H24" s="1">
+        <v>10</v>
+      </c>
+      <c r="I24" s="2">
+        <v>300000</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C25" s="1">
         <v>3</v>
       </c>
@@ -588,8 +744,17 @@
       <c r="E25" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H25" s="1">
+        <v>10</v>
+      </c>
+      <c r="I25" s="2">
+        <v>400000</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C26" s="1">
         <v>3</v>
       </c>
@@ -599,8 +764,17 @@
       <c r="E26" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H26" s="1">
+        <v>10</v>
+      </c>
+      <c r="I26" s="2">
+        <v>500000</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C27" s="1">
         <v>3</v>
       </c>
@@ -610,8 +784,17 @@
       <c r="E27" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H27" s="1">
+        <v>10</v>
+      </c>
+      <c r="I27" s="2">
+        <v>600000</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C28" s="1">
         <v>3</v>
       </c>
@@ -621,8 +804,17 @@
       <c r="E28" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H28" s="1">
+        <v>10</v>
+      </c>
+      <c r="I28" s="2">
+        <v>700000</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C29" s="1">
         <v>3</v>
       </c>
@@ -632,8 +824,17 @@
       <c r="E29" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H29" s="1">
+        <v>10</v>
+      </c>
+      <c r="I29" s="2">
+        <v>800000</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C30" s="1">
         <v>3</v>
       </c>
@@ -643,8 +844,17 @@
       <c r="E30" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="31" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="H30" s="1">
+        <v>10</v>
+      </c>
+      <c r="I30" s="2">
+        <v>900000</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C31" s="1">
         <v>3</v>
       </c>
@@ -652,6 +862,15 @@
         <v>1000000</v>
       </c>
       <c r="E31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H31" s="1">
+        <v>10</v>
+      </c>
+      <c r="I31" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="J31" s="1" t="s">
         <v>7</v>
       </c>
     </row>
